--- a/Research_agenda.xlsx
+++ b/Research_agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\GitHub\research_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B454BA69-7E06-4DFE-B714-E4CFADA029AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4925556D-DAAC-4656-BAD7-40562E1C22F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="99">
   <si>
     <t>Title</t>
   </si>
@@ -321,10 +321,13 @@
     <t>7. Published</t>
   </si>
   <si>
-    <t>Terminer, à soumettre</t>
-  </si>
-  <si>
-    <t>Terminer, à envoyer à Isabelle</t>
+    <t>Ajouter la réf sur le Chili, changer conceptual par state of the art</t>
+  </si>
+  <si>
+    <t>Attendre le retour des rapporteurs</t>
+  </si>
+  <si>
+    <t>En attente des retours d'Isabelle</t>
   </si>
 </sst>
 </file>
@@ -737,22 +740,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F3" t="s">
-        <v>40</v>
-      </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I3" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -760,19 +760,19 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I4" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -780,19 +780,25 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>71</v>
       </c>
       <c r="H5" t="s">
         <v>97</v>
       </c>
       <c r="I5" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -800,22 +806,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G6" t="s">
-        <v>73</v>
+      <c r="F6" t="s">
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -843,19 +849,22 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>90</v>
       </c>
+      <c r="G8" t="s">
+        <v>73</v>
+      </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -863,19 +872,19 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" t="s">
-        <v>71</v>
+        <v>90</v>
+      </c>
+      <c r="H9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -1347,7 +1356,7 @@
   </sheetData>
   <autoFilter ref="A1:I32" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I32">
-      <sortCondition ref="D1:D32"/>
+      <sortCondition ref="I1:I32"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Research_agenda.xlsx
+++ b/Research_agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\GitHub\research_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4925556D-DAAC-4656-BAD7-40562E1C22F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E61ABF-E3D4-400D-8B91-F50A901B39EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="100">
   <si>
     <t>Title</t>
   </si>
@@ -321,13 +321,16 @@
     <t>7. Published</t>
   </si>
   <si>
-    <t>Ajouter la réf sur le Chili, changer conceptual par state of the art</t>
-  </si>
-  <si>
     <t>Attendre le retour des rapporteurs</t>
   </si>
   <si>
     <t>En attente des retours d'Isabelle</t>
+  </si>
+  <si>
+    <t>En attente des retours de Damien</t>
+  </si>
+  <si>
+    <t>Soumis à Socio-Economic Review</t>
   </si>
 </sst>
 </file>
@@ -729,7 +732,7 @@
         <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I2" s="1">
         <v>1</v>
@@ -749,7 +752,7 @@
         <v>90</v>
       </c>
       <c r="H3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I3" s="1">
         <v>5</v>
@@ -769,7 +772,7 @@
         <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I4" s="1">
         <v>5</v>
@@ -795,7 +798,7 @@
         <v>71</v>
       </c>
       <c r="H5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I5" s="1">
         <v>5</v>

--- a/Research_agenda.xlsx
+++ b/Research_agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\GitHub\research_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E61ABF-E3D4-400D-8B91-F50A901B39EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67AD43B-C438-4E0D-917F-F66595F59C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="103">
   <si>
     <t>Title</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Big Five Personality Traits and Locus of Control: Challenges and Uses in the Global South</t>
   </si>
   <si>
-    <t>Handbook of</t>
-  </si>
-  <si>
     <t>Les Angles Morts des Inégalités</t>
   </si>
   <si>
@@ -327,10 +324,22 @@
     <t>En attente des retours d'Isabelle</t>
   </si>
   <si>
-    <t>En attente des retours de Damien</t>
-  </si>
-  <si>
     <t>Soumis à Socio-Economic Review</t>
+  </si>
+  <si>
+    <t>Soumis à World Development</t>
+  </si>
+  <si>
+    <t>Retours à la fin mars</t>
+  </si>
+  <si>
+    <t>Retour après le 23 mars</t>
+  </si>
+  <si>
+    <t>Envoyé à Ralitza</t>
+  </si>
+  <si>
+    <t>Avec les éditrices</t>
   </si>
 </sst>
 </file>
@@ -712,10 +721,10 @@
         <v>8</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -723,19 +732,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
       </c>
       <c r="H2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -743,19 +755,19 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I3" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -763,19 +775,22 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="G4" t="s">
+        <v>72</v>
       </c>
       <c r="H4" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="I4" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -783,25 +798,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="I5" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -809,22 +818,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I6" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -832,19 +838,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I7" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -852,22 +858,19 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="I8" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -875,19 +878,25 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>90</v>
       </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>70</v>
+      </c>
       <c r="H9" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="I9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
@@ -895,19 +904,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="H10" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -915,19 +927,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" t="s">
-        <v>35</v>
-      </c>
       <c r="G11" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="H11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -935,16 +950,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
         <v>41</v>
       </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
       <c r="D12" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -952,16 +967,16 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -969,16 +984,16 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -986,16 +1001,16 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1003,19 +1018,19 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
@@ -1026,56 +1041,68 @@
         <v>11</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E17" s="1">
         <v>2026</v>
       </c>
-      <c r="F17" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H17" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E18" s="1">
         <v>2026</v>
       </c>
-      <c r="F18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H18" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" s="1">
         <v>2026</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="H19" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,10 +1110,10 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E20" s="1">
         <v>2022</v>
@@ -1095,10 +1122,10 @@
         <v>7</v>
       </c>
       <c r="G20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
@@ -1109,7 +1136,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" s="1">
         <v>2022</v>
@@ -1118,10 +1145,10 @@
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
@@ -1129,10 +1156,10 @@
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" s="1">
         <v>2024</v>
@@ -1141,10 +1168,10 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>9</v>
       </c>
@@ -1155,7 +1182,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" s="1">
         <v>2025</v>
@@ -1164,10 +1191,10 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
@@ -1175,10 +1202,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E24" s="1">
         <v>2025</v>
@@ -1187,10 +1214,10 @@
         <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
@@ -1201,7 +1228,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25" s="1">
         <v>2025</v>
@@ -1210,10 +1237,10 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
@@ -1224,7 +1251,7 @@
         <v>11</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E26" s="1">
         <v>2026</v>
@@ -1233,127 +1260,127 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="B27" t="s">
-        <v>52</v>
-      </c>
       <c r="C27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E27" s="1">
         <v>2026</v>
       </c>
       <c r="F27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>54</v>
       </c>
-      <c r="C28" t="s">
-        <v>55</v>
-      </c>
       <c r="D28" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E28" s="1">
         <v>2025</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" t="s">
         <v>56</v>
       </c>
-      <c r="C29" t="s">
-        <v>57</v>
-      </c>
       <c r="D29" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E29" s="1">
         <v>2025</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" t="s">
         <v>58</v>
       </c>
-      <c r="C30" t="s">
-        <v>59</v>
-      </c>
       <c r="D30" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E30" s="1">
         <v>2025</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" t="s">
         <v>75</v>
       </c>
-      <c r="B31" t="s">
-        <v>76</v>
-      </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E31" s="1">
         <v>2024</v>
       </c>
       <c r="F31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="B32" t="s">
         <v>78</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>79</v>
       </c>
-      <c r="C32" t="s">
-        <v>80</v>
-      </c>
       <c r="D32" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E32" s="1">
         <v>2024</v>
       </c>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/Research_agenda.xlsx
+++ b/Research_agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\GitHub\research_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67AD43B-C438-4E0D-917F-F66595F59C7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E8A990-2A3D-4380-AEE5-A33C27553C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="102">
   <si>
     <t>Title</t>
   </si>
@@ -120,24 +120,15 @@
     <t>Girollet, Natal</t>
   </si>
   <si>
-    <t>Review of Social Economy</t>
-  </si>
-  <si>
     <t>She Works Hard for the Money: Debt Burden and Labour Supply in India</t>
   </si>
   <si>
-    <t>Feminist Economics</t>
-  </si>
-  <si>
     <t>Tangled Up in Debt: Household Rollover Debt Strategies and Spending in Rural India</t>
   </si>
   <si>
     <t>Natal</t>
   </si>
   <si>
-    <t>Development and Change</t>
-  </si>
-  <si>
     <t>Unveiling Inequality and Social Mobility in Rural South India: Household Income and Wealth Imbalances Between 2010 and 2026</t>
   </si>
   <si>
@@ -150,9 +141,6 @@
     <t>The Gender of Debt, Agrarian Transition and Social Reproduction</t>
   </si>
   <si>
-    <t>Journal of Peasant Studies</t>
-  </si>
-  <si>
     <t>Intra-Household Inequality and Recourse to debt</t>
   </si>
   <si>
@@ -252,9 +240,6 @@
     <t>ROIW (DR), JofEconIneq (rejected)</t>
   </si>
   <si>
-    <t>JDE (rejected), WBER (DR), JofPopEco (DR), OEP (rejected), JCE (rejected), WD (DR), FemEcon</t>
-  </si>
-  <si>
     <t>Blog</t>
   </si>
   <si>
@@ -321,15 +306,9 @@
     <t>Attendre le retour des rapporteurs</t>
   </si>
   <si>
-    <t>En attente des retours d'Isabelle</t>
-  </si>
-  <si>
     <t>Soumis à Socio-Economic Review</t>
   </si>
   <si>
-    <t>Soumis à World Development</t>
-  </si>
-  <si>
     <t>Retours à la fin mars</t>
   </si>
   <si>
@@ -340,6 +319,24 @@
   </si>
   <si>
     <t>Avec les éditrices</t>
+  </si>
+  <si>
+    <t>Soumis à Journal of Development Studies</t>
+  </si>
+  <si>
+    <t>Soumis à Oxford Development Studies</t>
+  </si>
+  <si>
+    <t>JDE (rejected), WBER (DR), JofPopEco (DR), OEP (rejected), JCE (rejected), WD (DR), FemEcon (DR), Rev Econ Hous</t>
+  </si>
+  <si>
+    <t>JPS</t>
+  </si>
+  <si>
+    <t>WD (DR), JDS</t>
+  </si>
+  <si>
+    <t>TWQ(DR), ODS</t>
   </si>
 </sst>
 </file>
@@ -721,10 +718,10 @@
         <v>8</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -732,22 +729,22 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
+        <v>84</v>
+      </c>
+      <c r="G2" t="s">
+        <v>99</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -755,16 +752,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I3" s="1">
         <v>2</v>
@@ -775,19 +772,19 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I4" s="1">
         <v>3</v>
@@ -798,19 +795,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I5" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -818,16 +815,19 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
+      </c>
+      <c r="G6" t="s">
+        <v>100</v>
       </c>
       <c r="H6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I6" s="1">
         <v>5</v>
@@ -838,16 +838,16 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="I7" s="1">
         <v>5</v>
@@ -858,16 +858,19 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>89</v>
+        <v>84</v>
+      </c>
+      <c r="G8" t="s">
+        <v>101</v>
       </c>
       <c r="H8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
@@ -884,16 +887,13 @@
         <v>28</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" t="s">
         <v>90</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" t="s">
-        <v>95</v>
       </c>
       <c r="I9" s="1">
         <v>5</v>
@@ -904,22 +904,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F10" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G10" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="H10" t="s">
-        <v>99</v>
+        <v>92</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -927,22 +927,22 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F11" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>100</v>
+        <v>93</v>
+      </c>
+      <c r="I11" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
@@ -950,16 +950,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -967,16 +967,16 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -984,16 +984,16 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1001,16 +1001,16 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1018,16 +1018,16 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -1041,13 +1041,13 @@
         <v>11</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E17" s="1">
         <v>2026</v>
       </c>
       <c r="H17" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I17" s="1">
         <v>5</v>
@@ -1064,13 +1064,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E18" s="1">
         <v>2026</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="I18" s="1">
         <v>5</v>
@@ -1087,7 +1087,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E19" s="1">
         <v>2026</v>
@@ -1096,7 +1096,7 @@
         <v>24</v>
       </c>
       <c r="H19" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="I19" s="1">
         <v>5</v>
@@ -1110,10 +1110,10 @@
         <v>6</v>
       </c>
       <c r="C20" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E20" s="1">
         <v>2022</v>
@@ -1122,7 +1122,7 @@
         <v>7</v>
       </c>
       <c r="G20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1136,7 +1136,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E21" s="1">
         <v>2022</v>
@@ -1145,7 +1145,7 @@
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -1156,10 +1156,10 @@
         <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E22" s="1">
         <v>2024</v>
@@ -1168,7 +1168,7 @@
         <v>7</v>
       </c>
       <c r="G22" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
@@ -1182,7 +1182,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E23" s="1">
         <v>2025</v>
@@ -1191,7 +1191,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
@@ -1202,10 +1202,10 @@
         <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E24" s="1">
         <v>2025</v>
@@ -1214,7 +1214,7 @@
         <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
@@ -1228,7 +1228,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E25" s="1">
         <v>2025</v>
@@ -1237,7 +1237,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
@@ -1251,7 +1251,7 @@
         <v>11</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E26" s="1">
         <v>2026</v>
@@ -1260,127 +1260,127 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E27" s="1">
         <v>2026</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
         <v>50</v>
       </c>
-      <c r="B28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" t="s">
-        <v>54</v>
-      </c>
       <c r="D28" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E28" s="1">
         <v>2025</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E29" s="1">
         <v>2025</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E30" s="1">
         <v>2025</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E31" s="1">
         <v>2024</v>
       </c>
       <c r="F31" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C32" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E32" s="1">
         <v>2024</v>
       </c>
       <c r="F32" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Research_agenda.xlsx
+++ b/Research_agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\GitHub\research_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E8A990-2A3D-4380-AEE5-A33C27553C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B937AE7-5061-4629-ADD1-E2A12B3D8ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -303,33 +303,15 @@
     <t>7. Published</t>
   </si>
   <si>
-    <t>Attendre le retour des rapporteurs</t>
-  </si>
-  <si>
     <t>Soumis à Socio-Economic Review</t>
   </si>
   <si>
-    <t>Retours à la fin mars</t>
-  </si>
-  <si>
-    <t>Retour après le 23 mars</t>
-  </si>
-  <si>
     <t>Envoyé à Ralitza</t>
   </si>
   <si>
     <t>Avec les éditrices</t>
   </si>
   <si>
-    <t>Soumis à Journal of Development Studies</t>
-  </si>
-  <si>
-    <t>Soumis à Oxford Development Studies</t>
-  </si>
-  <si>
-    <t>JDE (rejected), WBER (DR), JofPopEco (DR), OEP (rejected), JCE (rejected), WD (DR), FemEcon (DR), Rev Econ Hous</t>
-  </si>
-  <si>
     <t>JPS</t>
   </si>
   <si>
@@ -337,6 +319,24 @@
   </si>
   <si>
     <t>TWQ(DR), ODS</t>
+  </si>
+  <si>
+    <t>JDS</t>
+  </si>
+  <si>
+    <t>ODS</t>
+  </si>
+  <si>
+    <t>Soumis à Indian Journal of Labour Economics</t>
+  </si>
+  <si>
+    <t>JDE (rejected), WBER (DR), JofPopEco (DR), OEP (rejected), JCE (rejected), WD (DR), FemEcon (DR), Rev Econ Hous (DR), JID (DR)</t>
+  </si>
+  <si>
+    <t>Resoumis à RSE</t>
+  </si>
+  <si>
+    <t>Resoumis à D&amp;C</t>
   </si>
 </sst>
 </file>
@@ -738,7 +738,7 @@
         <v>84</v>
       </c>
       <c r="G2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H2" t="s">
         <v>78</v>
@@ -772,22 +772,19 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G4" t="s">
-        <v>68</v>
-      </c>
       <c r="H4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -795,19 +792,22 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>84</v>
       </c>
+      <c r="G5" t="s">
+        <v>68</v>
+      </c>
       <c r="H5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -815,19 +815,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G6" t="s">
-        <v>100</v>
-      </c>
       <c r="H6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I6" s="1">
         <v>5</v>
@@ -838,16 +835,19 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>84</v>
       </c>
+      <c r="G7" t="s">
+        <v>99</v>
+      </c>
       <c r="H7" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I7" s="1">
         <v>5</v>
@@ -858,19 +858,19 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
@@ -881,19 +881,19 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>85</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="I9" s="1">
         <v>5</v>
@@ -901,22 +901,22 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" t="s">
-        <v>98</v>
+        <v>85</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2026</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I10" s="1">
         <v>5</v>
@@ -924,22 +924,22 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="G11" t="s">
-        <v>67</v>
+        <v>85</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
       </c>
       <c r="H11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I11" s="1">
         <v>5</v>
@@ -950,16 +950,22 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="G12" t="s">
+        <v>94</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>96</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
@@ -967,33 +973,48 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
+      </c>
+      <c r="G13" t="s">
+        <v>95</v>
       </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>97</v>
+      </c>
+      <c r="I13" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>83</v>
+        <v>92</v>
+      </c>
+      <c r="I14" s="1">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
@@ -1001,10 +1022,10 @@
         <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>87</v>
@@ -1018,7 +1039,7 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -1030,79 +1051,58 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2026</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
-      </c>
-      <c r="I17" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2026</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s">
-        <v>94</v>
-      </c>
-      <c r="I18" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2026</v>
-      </c>
-      <c r="F19" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s">
-        <v>95</v>
-      </c>
-      <c r="I19" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>9</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
@@ -1240,7 +1240,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>46</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>46</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>46</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>46</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>69</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>72</v>
       </c>

--- a/Research_agenda.xlsx
+++ b/Research_agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\GitHub\research_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B937AE7-5061-4629-ADD1-E2A12B3D8ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AC5E40-8C24-4894-9355-85E1D851B1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="103">
   <si>
     <t>Title</t>
   </si>
@@ -267,9 +267,6 @@
     <t>Attendre les données 2026 pour continuer</t>
   </si>
   <si>
-    <t>À soumettre avant fin mars 2026</t>
-  </si>
-  <si>
     <t>Continuer le nettoyage des données</t>
   </si>
   <si>
@@ -303,9 +300,6 @@
     <t>7. Published</t>
   </si>
   <si>
-    <t>Soumis à Socio-Economic Review</t>
-  </si>
-  <si>
     <t>Envoyé à Ralitza</t>
   </si>
   <si>
@@ -337,6 +331,15 @@
   </si>
   <si>
     <t>Resoumis à D&amp;C</t>
+  </si>
+  <si>
+    <t>À soumettre avant fin aout 2026</t>
+  </si>
+  <si>
+    <t>SER (DR)</t>
+  </si>
+  <si>
+    <t>Soumis à Competition and Change</t>
   </si>
 </sst>
 </file>
@@ -721,7 +724,7 @@
         <v>76</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -735,13 +738,13 @@
         <v>58</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H2" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="I2" s="1">
         <v>1</v>
@@ -758,10 +761,10 @@
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I3" s="1">
         <v>2</v>
@@ -778,10 +781,10 @@
         <v>31</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I4" s="1">
         <v>2</v>
@@ -798,7 +801,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s">
         <v>68</v>
@@ -821,10 +824,13 @@
         <v>45</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="G6" t="s">
+        <v>101</v>
       </c>
       <c r="H6" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I6" s="1">
         <v>5</v>
@@ -841,13 +847,13 @@
         <v>11</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I7" s="1">
         <v>5</v>
@@ -864,13 +870,13 @@
         <v>28</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s">
         <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
@@ -887,13 +893,13 @@
         <v>31</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G9" t="s">
         <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I9" s="1">
         <v>5</v>
@@ -910,13 +916,13 @@
         <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E10" s="1">
         <v>2026</v>
       </c>
       <c r="H10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I10" s="1">
         <v>5</v>
@@ -933,13 +939,13 @@
         <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="1">
         <v>2026</v>
       </c>
       <c r="H11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I11" s="1">
         <v>5</v>
@@ -956,13 +962,13 @@
         <v>34</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" t="s">
         <v>94</v>
-      </c>
-      <c r="H12" t="s">
-        <v>96</v>
       </c>
       <c r="I12" s="1">
         <v>5</v>
@@ -973,19 +979,19 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" t="s">
         <v>95</v>
-      </c>
-      <c r="H13" t="s">
-        <v>97</v>
       </c>
       <c r="I13" s="1">
         <v>5</v>
@@ -1002,7 +1008,7 @@
         <v>11</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E14" s="1">
         <v>2026</v>
@@ -1011,7 +1017,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I14" s="1">
         <v>5</v>
@@ -1028,10 +1034,10 @@
         <v>37</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
@@ -1045,10 +1051,10 @@
         <v>31</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1062,10 +1068,10 @@
         <v>31</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1079,10 +1085,10 @@
         <v>31</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -1096,10 +1102,10 @@
         <v>31</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
@@ -1113,7 +1119,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E20" s="1">
         <v>2022</v>
@@ -1136,7 +1142,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E21" s="1">
         <v>2022</v>
@@ -1159,7 +1165,7 @@
         <v>56</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="1">
         <v>2024</v>
@@ -1182,7 +1188,7 @@
         <v>11</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23" s="1">
         <v>2025</v>
@@ -1205,7 +1211,7 @@
         <v>57</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E24" s="1">
         <v>2025</v>
@@ -1228,7 +1234,7 @@
         <v>19</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E25" s="1">
         <v>2025</v>
@@ -1251,7 +1257,7 @@
         <v>11</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E26" s="1">
         <v>2026</v>
@@ -1274,7 +1280,7 @@
         <v>45</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E27" s="1">
         <v>2026</v>
@@ -1294,7 +1300,7 @@
         <v>50</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E28" s="1">
         <v>2025</v>
@@ -1314,7 +1320,7 @@
         <v>52</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E29" s="1">
         <v>2025</v>
@@ -1334,7 +1340,7 @@
         <v>54</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30" s="1">
         <v>2025</v>
@@ -1354,7 +1360,7 @@
         <v>52</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1">
         <v>2024</v>
@@ -1374,7 +1380,7 @@
         <v>74</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E32" s="1">
         <v>2024</v>

--- a/Research_agenda.xlsx
+++ b/Research_agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\GitHub\research_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50AC5E40-8C24-4894-9355-85E1D851B1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AD0932-7AE0-4026-881D-5BFD8CE2DA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="102">
   <si>
     <t>Title</t>
   </si>
@@ -300,9 +300,6 @@
     <t>7. Published</t>
   </si>
   <si>
-    <t>Envoyé à Ralitza</t>
-  </si>
-  <si>
     <t>Avec les éditrices</t>
   </si>
   <si>
@@ -336,10 +333,10 @@
     <t>À soumettre avant fin aout 2026</t>
   </si>
   <si>
-    <t>SER (DR)</t>
-  </si>
-  <si>
-    <t>Soumis à Competition and Change</t>
+    <t>Soumis à Review of Social Economy</t>
+  </si>
+  <si>
+    <t>SER (DR), C&amp;C (DR), RSE</t>
   </si>
 </sst>
 </file>
@@ -741,10 +738,10 @@
         <v>83</v>
       </c>
       <c r="G2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I2" s="1">
         <v>1</v>
@@ -830,7 +827,7 @@
         <v>101</v>
       </c>
       <c r="H6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I6" s="1">
         <v>5</v>
@@ -850,10 +847,10 @@
         <v>83</v>
       </c>
       <c r="G7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I7" s="1">
         <v>5</v>
@@ -870,13 +867,13 @@
         <v>28</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
         <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I8" s="1">
         <v>5</v>
@@ -899,7 +896,7 @@
         <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I9" s="1">
         <v>5</v>
@@ -916,16 +913,10 @@
         <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E10" s="1">
         <v>2026</v>
-      </c>
-      <c r="H10" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -939,17 +930,11 @@
         <v>11</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E11" s="1">
         <v>2026</v>
       </c>
-      <c r="H11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="1">
-        <v>5</v>
-      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -965,10 +950,10 @@
         <v>85</v>
       </c>
       <c r="G12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I12" s="1">
         <v>5</v>
@@ -988,10 +973,10 @@
         <v>85</v>
       </c>
       <c r="G13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I13" s="1">
         <v>5</v>
@@ -1017,7 +1002,7 @@
         <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I14" s="1">
         <v>5</v>

--- a/Research_agenda.xlsx
+++ b/Research_agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnaud\Documents\GitHub\research_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88AD0932-7AE0-4026-881D-5BFD8CE2DA77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F636A0D7-7C22-4222-85BC-6BE8022DA391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="101">
   <si>
     <t>Title</t>
   </si>
@@ -312,21 +312,12 @@
     <t>TWQ(DR), ODS</t>
   </si>
   <si>
-    <t>JDS</t>
-  </si>
-  <si>
-    <t>ODS</t>
-  </si>
-  <si>
     <t>Soumis à Indian Journal of Labour Economics</t>
   </si>
   <si>
     <t>JDE (rejected), WBER (DR), JofPopEco (DR), OEP (rejected), JCE (rejected), WD (DR), FemEcon (DR), Rev Econ Hous (DR), JID (DR)</t>
   </si>
   <si>
-    <t>Resoumis à RSE</t>
-  </si>
-  <si>
     <t>Resoumis à D&amp;C</t>
   </si>
   <si>
@@ -337,6 +328,12 @@
   </si>
   <si>
     <t>SER (DR), C&amp;C (DR), RSE</t>
+  </si>
+  <si>
+    <t>Resoumis au JDS</t>
+  </si>
+  <si>
+    <t>Soumis à Oxford Development Studies</t>
   </si>
 </sst>
 </file>
@@ -741,7 +738,7 @@
         <v>90</v>
       </c>
       <c r="H2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I2" s="1">
         <v>1</v>
@@ -792,19 +789,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>83</v>
       </c>
       <c r="G5" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="H5" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="I5" s="1">
         <v>3</v>
@@ -815,22 +812,22 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>83</v>
       </c>
       <c r="G6" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I6" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -838,22 +835,22 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G7" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H7" t="s">
         <v>95</v>
       </c>
       <c r="I7" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -861,22 +858,22 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I8" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -884,39 +881,45 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="H9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2026</v>
+        <v>83</v>
+      </c>
+      <c r="G10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="1">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -924,7 +927,7 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -935,51 +938,48 @@
       <c r="E11" s="1">
         <v>2026</v>
       </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" s="1">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" t="s">
-        <v>94</v>
-      </c>
-      <c r="I13" s="1">
-        <v>5</v>
+        <v>87</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2026</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
@@ -987,7 +987,7 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -997,15 +997,6 @@
       </c>
       <c r="E14" s="1">
         <v>2026</v>
-      </c>
-      <c r="F14" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="1">
-        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
